--- a/evaluation_surveys/029_orange_challenge_evaluation_survey--evaluation_surveys.xlsx
+++ b/evaluation_surveys/029_orange_challenge_evaluation_survey--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Repeat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category Repeat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What do you like most about this event?</t>
+          <t>Select Multiple Repeat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date Repeat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time Repeat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note Repeat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How would you rate this event?</t>
+          <t>Rating Score Repeat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What areas of improvement would you like to suggest?</t>
+          <t>Improvement Areas Repeat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
